--- a/artfynd/S 3503-2023 artfynd.xlsx
+++ b/artfynd/S 3503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2159767</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55566698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6863045</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3498127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3788067</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/232358</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/250664</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/317233</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480664</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480993</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/522694</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/522695</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118152122</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/654944</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2263,6 +2338,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/654945</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2365,6 +2445,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/657448</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/661519</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,6 +2659,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/674175</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2674,6 +2769,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59608383</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2785,6 +2885,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/625693</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/639878</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2994,6 +3104,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/648574</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3099,6 +3214,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67735092</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3201,6 +3321,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/725284</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3303,6 +3428,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/739048</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3408,6 +3538,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67735100</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3515,6 +3650,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/758154</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3617,6 +3757,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/784329</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3719,6 +3864,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/790463</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3821,6 +3971,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/845682</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3934,6 +4089,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65641951</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4039,6 +4199,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67735087</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4148,6 +4313,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/877976</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4261,6 +4431,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/877977</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4374,6 +4549,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/879756</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4476,6 +4656,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/881802</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4589,6 +4774,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65641931</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4702,6 +4892,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67735084</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4807,6 +5002,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67735122</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4920,6 +5120,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67735147</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5027,6 +5232,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/750933</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5134,6 +5344,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/750934</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5236,6 +5451,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/757878</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5338,6 +5558,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/762005</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5444,6 +5669,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/707671</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5546,6 +5776,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/709267</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5648,6 +5883,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/726138</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5750,6 +5990,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/726832</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5852,6 +6097,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/745146</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5954,6 +6204,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1054023</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6059,6 +6314,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67689950</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6161,6 +6421,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1577766</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6270,6 +6535,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67689948</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6372,6 +6642,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1746963</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6479,6 +6754,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2121878</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6581,6 +6861,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2134619</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6674,6 +6959,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2078090</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6776,6 +7066,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1906173</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6898,6 +7193,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13480113</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7006,6 +7306,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7261979</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7117,6 +7422,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2929712</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7219,6 +7529,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2987808</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7326,6 +7641,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2432708</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7428,6 +7748,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2434596</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7545,6 +7870,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70502614</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7662,6 +7992,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70502668</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7779,6 +8114,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70502699</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7898,6 +8238,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116775812</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8000,6 +8345,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3507258</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8110,6 +8460,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83595600</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8220,6 +8575,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83597109</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8330,6 +8690,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83597121</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8440,6 +8805,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83597236</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8550,6 +8920,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83597246</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8660,6 +9035,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83597248</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8775,6 +9155,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83599247</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8882,6 +9267,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3256197</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8983,6 +9373,11 @@
           <t>Blekinges flora (2006)</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80348024</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9094,6 +9489,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85377566</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9191,6 +9591,11 @@
           <t>Blekinges flora (2006)</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80347955</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9302,6 +9707,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4222809</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9403,6 +9813,11 @@
           <t>Blekinges flora (2006)</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80347991</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9504,6 +9919,11 @@
           <t>Blekinges flora (2006)</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80347933</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9606,6 +10026,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5285425</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9708,6 +10133,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5767963</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9813,6 +10243,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67735103</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9921,6 +10356,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6144619</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10023,6 +10463,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6203095</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10130,6 +10575,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6203097</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10245,6 +10695,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118376863</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10343,6 +10798,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6224537</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10445,6 +10905,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6702730</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10547,8 +11012,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6703390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>